--- a/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0002T0006Z000C1N38_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0002T0006Z000C1N38_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>50.63724518715339</v>
+        <v>8.228552342912426</v>
       </c>
       <c r="D2" t="n">
-        <v>50.27742712245816</v>
+        <v>8.170081907399451</v>
       </c>
       <c r="E2" t="n">
-        <v>9.817647278561939</v>
+        <v>1.595367682766315</v>
       </c>
       <c r="F2" t="n">
-        <v>13.82047173540098</v>
+        <v>2.245826657002659</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>27.0101970602556</v>
+        <v>4.389157022291535</v>
       </c>
       <c r="D3" t="n">
-        <v>27.6680777039092</v>
+        <v>4.496062626885246</v>
       </c>
       <c r="E3" t="n">
-        <v>9.817647278561939</v>
+        <v>1.595367682766315</v>
       </c>
       <c r="F3" t="n">
-        <v>13.82047173540098</v>
+        <v>2.245826657002659</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>33.42336425963591</v>
+        <v>5.431296692190836</v>
       </c>
       <c r="D4" t="n">
-        <v>33.66095970775295</v>
+        <v>5.469905952509855</v>
       </c>
       <c r="E4" t="n">
-        <v>9.817647278561939</v>
+        <v>1.595367682766315</v>
       </c>
       <c r="F4" t="n">
-        <v>13.82047173540098</v>
+        <v>2.245826657002659</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>26.25429261247413</v>
+        <v>4.266322549527047</v>
       </c>
       <c r="D5" t="n">
-        <v>11.65167354737249</v>
+        <v>1.89339695144803</v>
       </c>
       <c r="E5" t="n">
-        <v>9.817647278561939</v>
+        <v>1.595367682766315</v>
       </c>
       <c r="F5" t="n">
-        <v>13.82047173540098</v>
+        <v>2.245826657002659</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
